--- a/excels/negociaciones_stata.xlsx
+++ b/excels/negociaciones_stata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conasamigobmx-my.sharepoint.com/personal/hector_soto_conasami_gob_mx/Documents/Escritorio/CAEL/Informes/Negociación laboral/excels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{3BBC8879-DF7E-4ADA-AAD8-7252CEF70536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEF96B2C-076D-4F75-8514-EDDFDD2F1A3D}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{B474DE53-D5B3-43BC-BC9D-BFFE3B91024D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3597FC21-7D3C-4439-9B43-123974C8346E}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="16395" tabRatio="801" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="entidad" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,6 @@
     <author>Arturo Lomeli Zenteno</author>
   </authors>
   <commentList>
-    <comment ref="S44" authorId="0" shapeId="0" xr:uid="{61F98506-64D6-4C7F-8F6E-41F13E389A6A}">
-      <text/>
-    </comment>
     <comment ref="S45" authorId="0" shapeId="0" xr:uid="{FCC1D1EA-F739-4F69-8BF4-6B48541E11A3}">
       <text/>
     </comment>
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="142">
   <si>
     <t>fecha</t>
   </si>
@@ -435,9 +432,6 @@
     <t>2025m4</t>
   </si>
   <si>
-    <t>Arturo Lomeli Zenteno: SE CHECA CON EL BOLETIN STPS</t>
-  </si>
-  <si>
     <t>2025m5</t>
   </si>
   <si>
@@ -469,6 +463,9 @@
   </si>
   <si>
     <t>2026m3</t>
+  </si>
+  <si>
+    <t>2026m4</t>
   </si>
 </sst>
 </file>
@@ -540,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -555,8 +552,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -874,7 +872,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:AL460"/>
+  <dimension ref="A1:AL461"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.73046875" bestFit="1" customWidth="1"/>
@@ -49042,7 +49040,7 @@
         <v>1.994528846153</v>
       </c>
       <c r="L458" s="8">
-        <v>5.2045016460899998</v>
+        <v>5.4645104777869999</v>
       </c>
       <c r="M458" s="8">
         <v>9.5134838317889994</v>
@@ -49097,7 +49095,7 @@
         <v>10.019500000000001</v>
       </c>
       <c r="AE458" s="8">
-        <v>1.248422638064</v>
+        <v>1.9655919390779999</v>
       </c>
       <c r="AF458" s="8">
         <v>4.7642693370159996</v>
@@ -49112,7 +49110,7 @@
         <v>3.2399355007859998</v>
       </c>
       <c r="AJ458" s="8">
-        <v>2.9981332369609999</v>
+        <v>3.000229928849</v>
       </c>
     </row>
     <row r="459" spans="1:36" x14ac:dyDescent="0.45">
@@ -49134,7 +49132,7 @@
       <c r="F459" s="8"/>
       <c r="G459" s="8"/>
       <c r="H459" s="8">
-        <v>4.6569167538169998</v>
+        <v>4.32406765044</v>
       </c>
       <c r="I459" s="8">
         <v>2.306881322957</v>
@@ -49152,7 +49150,7 @@
         <v>6.2297551525139996</v>
       </c>
       <c r="N459" s="8">
-        <v>5.3760736737299997</v>
+        <v>5.3772540890340004</v>
       </c>
       <c r="O459" s="8"/>
       <c r="P459" s="8">
@@ -49222,91 +49220,193 @@
         <v>3</v>
       </c>
       <c r="D460" s="8">
-        <v>0.39227560366300002</v>
-      </c>
-      <c r="E460" s="8"/>
+        <v>1.081770252893</v>
+      </c>
+      <c r="E460" s="8">
+        <v>4.2311212121209998</v>
+      </c>
       <c r="F460" s="8">
         <v>4.7665792682920003</v>
       </c>
       <c r="G460" s="8"/>
       <c r="H460" s="8">
-        <v>2.8459672430579999</v>
+        <v>3.02701446323</v>
       </c>
       <c r="I460" s="8">
         <v>2.09434090909</v>
       </c>
       <c r="J460" s="8">
-        <v>4.1397704288019996</v>
+        <v>4.069081898066</v>
       </c>
       <c r="K460" s="8">
-        <v>2.2995744680849999</v>
+        <v>2.7673520408160002</v>
       </c>
       <c r="L460" s="8">
-        <v>1.9542022321420001</v>
+        <v>1.781908335896</v>
       </c>
       <c r="M460" s="8"/>
       <c r="N460" s="8">
-        <v>3.8132121088250002</v>
+        <v>3.891038383838</v>
       </c>
       <c r="O460" s="8"/>
       <c r="P460" s="8">
-        <v>4.4500368744510004</v>
+        <v>4.4077004291839996</v>
       </c>
       <c r="Q460" s="8">
-        <v>0.86865329972500005</v>
+        <v>0.97501225919400003</v>
       </c>
       <c r="R460" s="8">
-        <v>0.55881201992899998</v>
+        <v>0.72499426934</v>
       </c>
       <c r="S460" s="8">
-        <v>1.494163030303</v>
+        <v>1.397661258741</v>
       </c>
       <c r="T460" s="8">
         <v>1.733752025931</v>
       </c>
       <c r="U460" s="8"/>
       <c r="V460" s="8">
-        <v>2.4116587301579999</v>
+        <v>2.5360894283630002</v>
       </c>
       <c r="W460" s="8">
-        <v>6.9070515463910001</v>
+        <v>6.4451286173630002</v>
       </c>
       <c r="X460" s="8">
-        <v>3.5174905956110001</v>
+        <v>4.0142914323510004</v>
       </c>
       <c r="Y460" s="8">
-        <v>4.6716884226879998</v>
+        <v>3.6734801635990002</v>
       </c>
       <c r="Z460" s="8">
         <v>2.1605625000000002</v>
       </c>
       <c r="AA460" s="8">
-        <v>3.8134500836580001</v>
+        <v>3.372959858702</v>
       </c>
       <c r="AB460" s="8">
-        <v>0.287465143526</v>
+        <v>0.50422336156900005</v>
       </c>
       <c r="AC460" s="8">
-        <v>2.9843336950619999</v>
+        <v>3.1600988009590001</v>
       </c>
       <c r="AD460" s="8"/>
       <c r="AE460" s="8">
-        <v>0.95083446549799999</v>
+        <v>1.752988555078</v>
       </c>
       <c r="AF460" s="8">
-        <v>3.3762738752949999</v>
+        <v>3.9537648530329998</v>
       </c>
       <c r="AG460" s="8">
-        <v>0.40037868525800002</v>
+        <v>0.49984279557799999</v>
       </c>
       <c r="AH460" s="8">
         <v>-0.24204633204600001</v>
       </c>
       <c r="AI460" s="8">
-        <v>4.7525692622950002</v>
+        <v>4.5914267425319997</v>
       </c>
       <c r="AJ460" s="8">
-        <v>2.5229104284139998</v>
+        <v>2.4868221269399999</v>
+      </c>
+    </row>
+    <row r="461" spans="1:36" x14ac:dyDescent="0.45">
+      <c r="A461" s="4">
+        <v>46113</v>
+      </c>
+      <c r="B461" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C461" s="5">
+        <v>4</v>
+      </c>
+      <c r="D461" s="8">
+        <v>5.2467142857139999</v>
+      </c>
+      <c r="E461" s="8">
+        <v>5.6948712121209999</v>
+      </c>
+      <c r="F461" s="8">
+        <v>1.954333333333</v>
+      </c>
+      <c r="G461" s="8">
+        <v>7.5173617021270003</v>
+      </c>
+      <c r="H461" s="8">
+        <v>-0.16815730337000001</v>
+      </c>
+      <c r="I461" s="8">
+        <v>-0.103450980392</v>
+      </c>
+      <c r="J461" s="8"/>
+      <c r="K461" s="8">
+        <v>12.118288732393999</v>
+      </c>
+      <c r="L461" s="8">
+        <v>2.737164588528</v>
+      </c>
+      <c r="M461" s="8"/>
+      <c r="N461" s="8">
+        <v>2.118000953288</v>
+      </c>
+      <c r="O461" s="8">
+        <v>3.3144547770699999</v>
+      </c>
+      <c r="P461" s="8">
+        <v>4.0582884462150002</v>
+      </c>
+      <c r="Q461" s="8">
+        <v>0.88449695585900001</v>
+      </c>
+      <c r="R461" s="8">
+        <v>1.5284672495139999</v>
+      </c>
+      <c r="S461" s="8">
+        <v>2.052220902612</v>
+      </c>
+      <c r="T461" s="8">
+        <v>0.42355681818099999</v>
+      </c>
+      <c r="U461" s="8"/>
+      <c r="V461" s="8">
+        <v>1.895437737487</v>
+      </c>
+      <c r="W461" s="8">
+        <v>0.119783928571</v>
+      </c>
+      <c r="X461" s="8">
+        <v>2.2229826429399999</v>
+      </c>
+      <c r="Y461" s="8">
+        <v>1.302234326824</v>
+      </c>
+      <c r="Z461" s="8"/>
+      <c r="AA461" s="8">
+        <v>-0.11865124208400001</v>
+      </c>
+      <c r="AB461" s="8">
+        <v>1.4199609756089999</v>
+      </c>
+      <c r="AC461" s="8">
+        <v>2.103477876106</v>
+      </c>
+      <c r="AD461" s="8">
+        <v>1.764568047337</v>
+      </c>
+      <c r="AE461" s="8">
+        <v>0.71273504273499999</v>
+      </c>
+      <c r="AF461" s="8">
+        <v>2.9396958270479998</v>
+      </c>
+      <c r="AG461" s="8">
+        <v>1.1930849056599999</v>
+      </c>
+      <c r="AH461" s="8"/>
+      <c r="AI461" s="8">
+        <v>3.0270744000000001</v>
+      </c>
+      <c r="AJ461" s="8">
+        <v>0.67598969416800003</v>
       </c>
     </row>
   </sheetData>
@@ -49320,7 +49420,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:AF460"/>
+  <dimension ref="A1:AF461"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.86328125" customWidth="1"/>
@@ -65301,7 +65401,7 @@
         <v>0.405470292437</v>
       </c>
       <c r="E458" s="8">
-        <v>4.5294776563569998</v>
+        <v>4.5428158086610004</v>
       </c>
       <c r="F458">
         <v>4</v>
@@ -65313,13 +65413,13 @@
         <v>20483</v>
       </c>
       <c r="I458">
-        <v>123995</v>
+        <v>124805</v>
       </c>
       <c r="J458" s="8">
         <v>4.2121442171550001</v>
       </c>
       <c r="K458" s="8">
-        <v>8.4925050203629997</v>
+        <v>8.5063488642280003</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.45">
@@ -65332,11 +65432,11 @@
       <c r="C459" s="5">
         <v>2026</v>
       </c>
-      <c r="D459" s="12">
-        <v>-2.1290175171E-2</v>
+      <c r="D459" s="8">
+        <v>-2.1504285713999999E-2</v>
       </c>
       <c r="E459" s="8">
-        <v>2.7695075292540001</v>
+        <v>2.769586150166</v>
       </c>
       <c r="F459">
         <v>8</v>
@@ -65345,16 +65445,16 @@
         <v>354</v>
       </c>
       <c r="H459">
-        <v>2626</v>
+        <v>3500</v>
       </c>
       <c r="I459">
         <v>210313</v>
       </c>
       <c r="J459" s="8">
-        <v>4.0008910891080003</v>
+        <v>4.0006685714280001</v>
       </c>
       <c r="K459" s="8">
-        <v>6.9039640916150002</v>
+        <v>6.9040458744819997</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.45">
@@ -65371,25 +65471,60 @@
         <v>0.71152370216500005</v>
       </c>
       <c r="E460" s="8">
-        <v>2.9164451173970001</v>
+        <v>2.8954992749759998</v>
       </c>
       <c r="F460">
         <v>6</v>
       </c>
       <c r="G460">
-        <v>230</v>
+        <v>375</v>
       </c>
       <c r="H460">
         <v>33710</v>
       </c>
       <c r="I460">
-        <v>145957</v>
+        <v>178615</v>
       </c>
       <c r="J460" s="8">
         <v>5.3309332542270003</v>
       </c>
       <c r="K460" s="8">
-        <v>7.636989455798</v>
+        <v>7.6150828317889996</v>
+      </c>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A461" s="4">
+        <v>46113</v>
+      </c>
+      <c r="B461" s="5">
+        <v>4</v>
+      </c>
+      <c r="C461" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D461" s="8">
+        <v>-0.42611120553699999</v>
+      </c>
+      <c r="E461" s="8">
+        <v>1.8689358587280001</v>
+      </c>
+      <c r="F461">
+        <v>8</v>
+      </c>
+      <c r="G461">
+        <v>201</v>
+      </c>
+      <c r="H461">
+        <v>81192</v>
+      </c>
+      <c r="I461">
+        <v>127188</v>
+      </c>
+      <c r="J461" s="8">
+        <v>4.0034362991419998</v>
+      </c>
+      <c r="K461" s="8">
+        <v>6.4005785923199996</v>
       </c>
     </row>
   </sheetData>
@@ -65403,7 +65538,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:G460"/>
+  <dimension ref="A1:G461"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.73046875" bestFit="1" customWidth="1"/>
@@ -75938,13 +76073,13 @@
         <v>242</v>
       </c>
       <c r="E458">
-        <v>144478</v>
+        <v>145288</v>
       </c>
       <c r="F458" s="8">
-        <v>7.8856677833299997</v>
+        <v>7.9009430923400004</v>
       </c>
       <c r="G458" s="8">
-        <v>3.944807029443</v>
+        <v>3.959524358515</v>
       </c>
     </row>
     <row r="459" spans="1:7" x14ac:dyDescent="0.45">
@@ -75961,13 +76096,13 @@
         <v>362</v>
       </c>
       <c r="E459">
-        <v>212939</v>
+        <v>213813</v>
       </c>
       <c r="F459" s="8">
-        <v>6.868162901112</v>
+        <v>6.8565192013580001</v>
       </c>
       <c r="G459" s="8">
-        <v>2.7350909368409999</v>
+        <v>2.7238975506630001</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.45">
@@ -75981,16 +76116,39 @@
         <v>3</v>
       </c>
       <c r="D460">
-        <v>236</v>
+        <v>381</v>
       </c>
       <c r="E460">
-        <v>179667</v>
+        <v>212325</v>
       </c>
       <c r="F460" s="8">
-        <v>7.204315928912</v>
+        <v>7.2524374425989997</v>
       </c>
       <c r="G460" s="8">
-        <v>2.502746993048</v>
+        <v>2.5487581160950001</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A461" s="4">
+        <v>46113</v>
+      </c>
+      <c r="B461" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C461" s="5">
+        <v>4</v>
+      </c>
+      <c r="D461">
+        <v>209</v>
+      </c>
+      <c r="E461">
+        <v>208380</v>
+      </c>
+      <c r="F461" s="8">
+        <v>5.4665696803910002</v>
+      </c>
+      <c r="G461" s="8">
+        <v>0.97470675208699997</v>
       </c>
     </row>
   </sheetData>
@@ -76675,13 +76833,13 @@
         <v>2026</v>
       </c>
       <c r="B40" s="3">
-        <v>840</v>
+        <v>1194</v>
       </c>
       <c r="C40" s="3">
-        <v>537084</v>
+        <v>779806</v>
       </c>
       <c r="D40" s="5">
-        <v>7.2543272188329997</v>
+        <v>6.7874865415240002</v>
       </c>
       <c r="E40" s="5">
         <v>2.9827855661310001</v>
@@ -76697,7 +76855,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:G409"/>
+  <dimension ref="A1:G410"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.73046875" bestFit="1" customWidth="1"/>
@@ -85847,16 +86005,16 @@
         <v>1</v>
       </c>
       <c r="D398">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E398">
-        <v>210953</v>
+        <v>209541</v>
       </c>
       <c r="F398" s="8">
-        <v>10.280668205714063</v>
+        <v>10.277977293226622</v>
       </c>
       <c r="G398" s="8">
-        <v>6.4638951173109103</v>
+        <v>6.4612973363081823</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.45">
@@ -85870,16 +86028,16 @@
         <v>2</v>
       </c>
       <c r="D399">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E399">
-        <v>194098</v>
+        <v>194091</v>
       </c>
       <c r="F399" s="8">
-        <v>8.0846027779781142</v>
+        <v>8.0844615669969304</v>
       </c>
       <c r="G399" s="8">
-        <v>4.1539277710227038</v>
+        <v>4.1537916954119414</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.45">
@@ -85893,16 +86051,16 @@
         <v>3</v>
       </c>
       <c r="D400">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E400">
-        <v>225830</v>
+        <v>225924</v>
       </c>
       <c r="F400" s="8">
-        <v>9.2365415135278575</v>
+        <v>9.2365055062764387</v>
       </c>
       <c r="G400" s="8">
-        <v>5.2363588793635758</v>
+        <v>5.2363241906780766</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.45">
@@ -85922,10 +86080,10 @@
         <v>168606</v>
       </c>
       <c r="F401" s="8">
-        <v>8.6307127267119856</v>
+        <v>8.6307127267119679</v>
       </c>
       <c r="G401" s="8">
-        <v>4.5195203040795189</v>
+        <v>4.519520304079518</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.45">
@@ -85945,10 +86103,10 @@
         <v>124786</v>
       </c>
       <c r="F402" s="8">
-        <v>8.2666247816261453</v>
+        <v>8.2666247816261418</v>
       </c>
       <c r="G402" s="8">
-        <v>3.6850192633053132</v>
+        <v>3.6850192633053056</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.45">
@@ -85968,10 +86126,10 @@
         <v>127971</v>
       </c>
       <c r="F403" s="8">
-        <v>10.116352064139527</v>
+        <v>10.11635206413953</v>
       </c>
       <c r="G403" s="8">
-        <v>5.5589209053865325</v>
+        <v>5.5589209053865298</v>
       </c>
     </row>
     <row r="404" spans="1:7" x14ac:dyDescent="0.45">
@@ -85991,10 +86149,10 @@
         <v>117598</v>
       </c>
       <c r="F404" s="8">
-        <v>9.2247871562441581</v>
+        <v>9.2247871562441546</v>
       </c>
       <c r="G404" s="8">
-        <v>5.5185305271393128</v>
+        <v>5.5185305271393208</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.45">
@@ -86014,10 +86172,10 @@
         <v>169989</v>
       </c>
       <c r="F405" s="8">
-        <v>8.5982795357346671</v>
+        <v>8.59827953573466</v>
       </c>
       <c r="G405" s="8">
-        <v>4.8561962311533504</v>
+        <v>4.8561962311533575</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.45">
@@ -86031,16 +86189,16 @@
         <v>9</v>
       </c>
       <c r="D406">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E406">
-        <v>92221</v>
+        <v>92238</v>
       </c>
       <c r="F406" s="8">
-        <v>8.8274381106255699</v>
+        <v>8.827469914785663</v>
       </c>
       <c r="G406" s="8">
-        <v>4.8835157835784617</v>
+        <v>4.88354643515114</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.45">
@@ -86057,13 +86215,13 @@
         <v>710</v>
       </c>
       <c r="E407">
-        <v>91597</v>
+        <v>91616</v>
       </c>
       <c r="F407" s="8">
-        <v>9.4719715711213297</v>
+        <v>9.4722938133077239</v>
       </c>
       <c r="G407" s="8">
-        <v>5.7020840470078671</v>
+        <v>5.7023951921364411</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.45">
@@ -86077,16 +86235,16 @@
         <v>11</v>
       </c>
       <c r="D408">
-        <v>642</v>
+        <v>715</v>
       </c>
       <c r="E408">
-        <v>97021</v>
+        <v>103767</v>
       </c>
       <c r="F408" s="8">
-        <v>7.7160830129559494</v>
+        <v>7.6595916813630494</v>
       </c>
       <c r="G408" s="8">
-        <v>3.7735286338284584</v>
+        <v>3.7191049614051432</v>
       </c>
     </row>
     <row r="409" spans="1:7" x14ac:dyDescent="0.45">
@@ -86096,20 +86254,43 @@
       <c r="B409" s="5">
         <v>2025</v>
       </c>
-      <c r="C409" s="13">
+      <c r="C409" s="5">
         <v>12</v>
       </c>
       <c r="D409">
-        <v>171</v>
+        <v>266</v>
       </c>
       <c r="E409">
-        <v>50376</v>
+        <v>65001</v>
       </c>
       <c r="F409" s="8">
-        <v>6.6615965936160082</v>
+        <v>7.2528521099675407</v>
       </c>
       <c r="G409" s="8">
-        <v>2.863918209286338</v>
+        <v>3.4341221160072841</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A410" s="4">
+        <v>46023</v>
+      </c>
+      <c r="B410" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C410" s="5">
+        <v>1</v>
+      </c>
+      <c r="D410">
+        <v>89</v>
+      </c>
+      <c r="E410">
+        <v>30216</v>
+      </c>
+      <c r="F410" s="8">
+        <v>8.5353213529256031</v>
+      </c>
+      <c r="G410" s="8">
+        <v>4.5707298794313349</v>
       </c>
     </row>
   </sheetData>
@@ -86122,7 +86303,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -86708,16 +86889,33 @@
         <v>2025</v>
       </c>
       <c r="B35" s="3">
-        <v>9668</v>
+        <v>9836</v>
       </c>
       <c r="C35" s="3">
-        <v>1671046</v>
+        <v>1691128</v>
       </c>
       <c r="D35" s="2">
-        <v>8.927040530302591</v>
+        <v>8.9204380803818495</v>
       </c>
       <c r="E35" s="2">
-        <v>4.9329106722168756</v>
+        <v>4.9273965904349053</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B36">
+        <v>89</v>
+      </c>
+      <c r="C36">
+        <v>30216</v>
+      </c>
+      <c r="D36">
+        <v>8.5353213529256031</v>
+      </c>
+      <c r="E36">
+        <v>4.5707298794313349</v>
       </c>
     </row>
   </sheetData>
@@ -88064,7 +88262,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2">
         <v>0</v>
@@ -88960,7 +89158,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2">
         <v>0</v>
@@ -89072,7 +89270,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L42" s="2">
         <v>1</v>
@@ -89183,40 +89381,38 @@
       <c r="J44" s="5">
         <v>2</v>
       </c>
-      <c r="K44" s="10">
+      <c r="K44" s="5">
         <v>5</v>
       </c>
-      <c r="L44" s="10">
-        <v>0</v>
-      </c>
-      <c r="M44" s="10">
-        <v>0</v>
-      </c>
-      <c r="N44" s="10">
-        <v>0</v>
-      </c>
-      <c r="O44" s="10">
+      <c r="L44" s="5">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5">
+        <v>0</v>
+      </c>
+      <c r="O44" s="5">
         <v>1</v>
       </c>
-      <c r="P44" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="10">
+      <c r="P44" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5">
         <v>4</v>
       </c>
-      <c r="R44" s="10">
-        <v>0</v>
-      </c>
-      <c r="S44" s="11" t="s">
-        <v>130</v>
-      </c>
+      <c r="R44" s="5">
+        <v>0</v>
+      </c>
+      <c r="S44" s="12"/>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="5">
         <v>2026</v>
       </c>
       <c r="B45" s="5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C45" s="5">
         <v>1</v>
@@ -89225,7 +89421,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="5">
         <v>1</v>
@@ -89234,7 +89430,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" s="5">
         <v>3</v>
@@ -89243,7 +89439,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L45" s="10">
         <v>0</v>
@@ -89266,9 +89462,7 @@
       <c r="R45" s="10">
         <v>3</v>
       </c>
-      <c r="S45" s="11" t="s">
-        <v>130</v>
-      </c>
+      <c r="S45" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -89282,7 +89476,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -90272,7 +90466,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B66">
         <v>2025</v>
@@ -90286,7 +90480,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B67">
         <v>2025</v>
@@ -90300,7 +90494,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B68">
         <v>2025</v>
@@ -90314,7 +90508,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B69">
         <v>2025</v>
@@ -90328,7 +90522,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B70">
         <v>2025</v>
@@ -90342,7 +90536,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B71">
         <v>2025</v>
@@ -90356,7 +90550,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B72">
         <v>2025</v>
@@ -90370,7 +90564,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B73">
         <v>2025</v>
@@ -90384,7 +90578,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B74">
         <v>2026</v>
@@ -90398,7 +90592,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B75">
         <v>2026</v>
@@ -90412,7 +90606,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B76">
         <v>2026</v>
@@ -90422,6 +90616,20 @@
       </c>
       <c r="E76">
         <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>141</v>
+      </c>
+      <c r="B77">
+        <v>2026</v>
+      </c>
+      <c r="C77">
+        <v>4</v>
+      </c>
+      <c r="E77">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -90431,23 +90639,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="131f92be-fc8f-4520-9a64-c4bcb115a629" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FF9D60EAC15C74AB5D052FF9D77E5BD" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f95571b9953812dd2fdc4cb3d4990df1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="131f92be-fc8f-4520-9a64-c4bcb115a629" xmlns:ns4="567dafe5-a41b-4f34-91e8-c3ec40d430cf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ccd401f49274f34ab9c1e94fafb5be50" ns3:_="" ns4:_="">
     <xsd:import namespace="131f92be-fc8f-4520-9a64-c4bcb115a629"/>
@@ -90688,10 +90879,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="131f92be-fc8f-4520-9a64-c4bcb115a629" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C76544A-111A-4344-9392-E6E1D277A5D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FAF1E6C-9342-454D-B4C8-C6EE5854F992}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="131f92be-fc8f-4520-9a64-c4bcb115a629"/>
+    <ds:schemaRef ds:uri="567dafe5-a41b-4f34-91e8-c3ec40d430cf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -90714,20 +90933,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FAF1E6C-9342-454D-B4C8-C6EE5854F992}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C76544A-111A-4344-9392-E6E1D277A5D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="131f92be-fc8f-4520-9a64-c4bcb115a629"/>
-    <ds:schemaRef ds:uri="567dafe5-a41b-4f34-91e8-c3ec40d430cf"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>